--- a/i18n/nisyros-wines-translation.xlsx
+++ b/i18n/nisyros-wines-translation.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Translate every English string in column `en` into Greek in column `el`.</t>
+          <t>Column `el` is pre-filled with a first-draft Greek translation. Please review, refine and overwrite where needed.</t>
         </is>
       </c>
     </row>
@@ -540,166 +540,173 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>The draft was produced as a starting point — a native Greek speaker familiar with wine terminology should validate every row, especially manifesto bodies, wine tasting notes, and faces captions where the poetic register matters.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>How it's organized</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Each sheet groups related strings. Order follows the user's path through the site:</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. README              — this page</t>
+          <t>Each sheet groups related strings. Order follows the user's path through the site:</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Static HTML         — nav, intro slides, fixed UI labels (Story/Winemaking/…), aria labels</t>
+          <t xml:space="preserve">  1. README              — this page</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. CMS — Config        — hero, full manifesto, contact texts, footer, collection descriptions</t>
+          <t xml:space="preserve">  2. Static HTML         — nav, intro slides, fixed UI labels (Story/Winemaking/…), aria labels</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. CMS — Wines         — per-wine content (name, subtitle, body, specs, detail fields) × 5 wines</t>
+          <t xml:space="preserve">  3. CMS — Config        — hero, full manifesto, contact texts, footer, collection descriptions</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. CMS — Faces         — gallery photo captions (label + text) × ~27 photos</t>
+          <t xml:space="preserve">  4. CMS — Wines         — per-wine content (name, subtitle, body, specs, detail fields) × 5 wines</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  5. CMS — Faces         — gallery photo captions (label + text) × ~27 photos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  6. SEO                 — page title, meta description, social tags, structured data</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Guidelines</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>• Tone: short declarative sentences, manifesto-like, no marketing fluff.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>• Multi-line titles split with slashes ("Wines / from the / Edge") render one word per line — keep that rhythm in Greek.</t>
+          <t>• Tone: short declarative sentences, manifesto-like, no marketing fluff.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>• Brand names stay in latin script: Nisyros Wines, Monopàtia, Nereides, Volcanica, 3,2,1, 40 Milia Konda, Roudià, Apiri, Atmida.</t>
+          <t>• Multi-line titles split with slashes ("Wines / from the / Edge") render one word per line — keep that rhythm in Greek.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>• Grape varieties: keep latin (Athiri, Mandilaria, Assyrtiko, Mavrothiriko) unless the brand prefers Greek script — confirm with Nicola.</t>
+          <t>• Brand names stay in latin script: Nisyros Wines, Monopàtia, Nereides, Volcanica, 3,2,1, 40 Milia Konda, Roudià, Apiri, Atmida.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>• Geographic names: use the natural Greek form — Νίσυρος, Δωδεκάνησα, Αιγαίο, Ρόδος, Έμπωνας, Σιάννα.</t>
+          <t>• Grape varieties: keep latin (Athiri, Mandilaria, Assyrtiko, Mavrothiriko) unless the brand prefers Greek script — confirm with Nicola.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>• Numbers, percentages, volumes, alcohol degrees, altitudes stay as-is.</t>
+          <t>• Geographic names: use the natural Greek form — Νίσυρος, Δωδεκάνησα, Αιγαίο, Ρόδος, Έμπωνας, Σιάννα.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>• Body text with `||` separators: keep the `||` exactly where it is. Each part is rendered in its own block (Story / Winemaking / Tasting Notes).</t>
+          <t>• Numbers, percentages, volumes, alcohol degrees, altitudes stay as-is.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>• Specs separated by `|`: keep the `|` separators between items.</t>
+          <t>• Body text with `||` separators: keep the `||` exactly where it is. Each part is rendered in its own block (Story / Winemaking / Tasting Notes).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>• If a string contains `\n`, that is a literal newline marker — keep it.</t>
+          <t>• Specs separated by `|`: keep the `|` separators between items.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>• If a string contains `\n`, that is a literal newline marker — keep it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>• If meaning is ambiguous, write a question in the `notes` column.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-    </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Save this file as-is when done. The developer copies `el` values back into the codebase and into the Google Sheet's new `_el` columns.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-    </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Generated from the live Google Sheet — re-run i18n/build_translation_xlsx.py to refresh.</t>
         </is>
@@ -772,7 +779,11 @@
           <t>Manifesto</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Μανιφέστο</t>
+        </is>
+      </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Top nav link</t>
@@ -790,7 +801,11 @@
           <t>Wines</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Κρασιά</t>
+        </is>
+      </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Top nav link</t>
@@ -808,7 +823,11 @@
           <t>Faces</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr"/>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Πρόσωπα</t>
+        </is>
+      </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Top nav link</t>
@@ -826,7 +845,11 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Επικοινωνία</t>
+        </is>
+      </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Top nav link</t>
@@ -844,7 +867,11 @@
           <t>EN</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr"/>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Language switcher label (English)</t>
@@ -862,7 +889,11 @@
           <t>EL</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>ΕΛ</t>
+        </is>
+      </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Language switcher label (Greek) — likely 'ΕΛ'</t>
@@ -880,7 +911,11 @@
           <t>Menu</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Μενού</t>
+        </is>
+      </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Hamburger button aria-label (screen reader)</t>
@@ -905,7 +940,11 @@
           <t>5 Wines.</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>5 Κρασιά.</t>
+        </is>
+      </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Big line 1, red</t>
@@ -923,7 +962,11 @@
           <t>2 Vintages.</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>2 Σοδειές.</t>
+        </is>
+      </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Big line 2</t>
@@ -941,7 +984,11 @@
           <t>3 Collections.</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr"/>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>3 Συλλογές.</t>
+        </is>
+      </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Big line 3</t>
@@ -959,7 +1006,11 @@
           <t>Discover &gt;</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr"/>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Ανακαλύψτε &gt;</t>
+        </is>
+      </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
           <t>CTA button</t>
@@ -984,7 +1035,11 @@
           <t>Story</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Ιστορία</t>
+        </is>
+      </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Wine card — label above part 1 of body</t>
@@ -1002,7 +1057,11 @@
           <t>Winemaking</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr"/>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Οινοποίηση</t>
+        </is>
+      </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Wine card — label above part 2 of body</t>
@@ -1020,7 +1079,11 @@
           <t>Tasting Notes</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr"/>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Σημειώσεις Γεύσης</t>
+        </is>
+      </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Wine card — label above part 3 of body</t>
@@ -1045,7 +1108,11 @@
           <t>Vintages</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr"/>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Σοδειές</t>
+        </is>
+      </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Wine detail row label</t>
@@ -1063,7 +1130,11 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr"/>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Τύπος</t>
+        </is>
+      </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Wine detail row label</t>
@@ -1081,7 +1152,11 @@
           <t>Variety</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr"/>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Ποικιλία</t>
+        </is>
+      </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Wine detail row label</t>
@@ -1099,7 +1174,11 @@
           <t>Appellation</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr"/>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Ονομασία</t>
+        </is>
+      </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Wine detail row label</t>
@@ -1117,7 +1196,11 @@
           <t>Origin</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr"/>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Προέλευση</t>
+        </is>
+      </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Wine detail row label</t>
@@ -1135,7 +1218,11 @@
           <t>Altitude</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Υψόμετρο</t>
+        </is>
+      </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Wine detail row label</t>
@@ -1153,7 +1240,11 @@
           <t>Soil</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Έδαφος</t>
+        </is>
+      </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Wine detail row label</t>
@@ -1171,7 +1262,11 @@
           <t>Vinification</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr"/>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Μέθοδος</t>
+        </is>
+      </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Wine detail row label</t>
@@ -1189,7 +1284,11 @@
           <t>Production</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr"/>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Παραγωγή</t>
+        </is>
+      </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Wine detail row label</t>
@@ -1207,7 +1306,11 @@
           <t>Collection</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr"/>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Συλλογή</t>
+        </is>
+      </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
           <t>Appended after name (e.g. "Volcanica Collection"). In Greek likely "Συλλογή" placed BEFORE the name — flag if word order matters.</t>
@@ -1225,7 +1328,11 @@
           <t>alc.{n}% by vol.</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr"/>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>αλκ. {n}% vol.</t>
+        </is>
+      </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Wine card footer template. Keep the {n} placeholder.</t>
@@ -1250,7 +1357,11 @@
           <t>Our Collections</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr"/>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Οι Συλλογές μας</t>
+        </is>
+      </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Small eyebrow over title</t>
@@ -1268,7 +1379,11 @@
           <t>Three Directions</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr"/>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Τρεις Κατευθύνσεις</t>
+        </is>
+      </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
           <t>Big title — collection descriptions live in CMS Config</t>
@@ -1293,7 +1408,11 @@
           <t>Faces</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr"/>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Πρόσωπα</t>
+        </is>
+      </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
           <t>Section title line 1</t>
@@ -1311,7 +1430,11 @@
           <t>&amp; Places</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr"/>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>&amp; Τόποι</t>
+        </is>
+      </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
           <t>Section title line 2</t>
@@ -1329,7 +1452,11 @@
           <t>The island. The people. The bottles. What the cellar smells like at five in the morning.</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr"/>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Το νησί. Οι άνθρωποι. Τα μπουκάλια. Πώς μυρίζει το οινοποιείο στις πέντε το πρωί.</t>
+        </is>
+      </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
           <t>Section intro caption</t>
@@ -1347,7 +1474,11 @@
           <t>Close</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr"/>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Κλείσιμο</t>
+        </is>
+      </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Lightbox close button — aria label</t>
@@ -1365,7 +1496,11 @@
           <t>Previous</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr"/>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Προηγούμενο</t>
+        </is>
+      </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
           <t>Lightbox previous button — aria label</t>
@@ -1383,7 +1518,11 @@
           <t>Next</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr"/>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Επόμενο</t>
+        </is>
+      </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
           <t>Lightbox next button — aria label</t>
@@ -1408,7 +1547,11 @@
           <t>Find</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr"/>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Βρείτε</t>
+        </is>
+      </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
           <t>Big section title — line 1</t>
@@ -1426,7 +1569,11 @@
           <t>Us</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr"/>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>μας</t>
+        </is>
+      </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
           <t>Big section title — line 2</t>
@@ -1444,7 +1591,11 @@
           <t>Location</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr"/>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Τοποθεσία</t>
+        </is>
+      </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
           <t>Block label</t>
@@ -1462,7 +1613,11 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr"/>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Επικοινωνία</t>
+        </is>
+      </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
           <t>Block label</t>
@@ -1480,7 +1635,11 @@
           <t>Visits &amp; Tastings</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr"/>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Επισκέψεις &amp; Γευσιγνωσίες</t>
+        </is>
+      </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
           <t>Block label</t>
@@ -1498,7 +1657,11 @@
           <t>Follow</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr"/>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Ακολουθήστε</t>
+        </is>
+      </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
           <t>Block label</t>
@@ -1516,7 +1679,11 @@
           <t>Trade &amp; Distribution</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr"/>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Εμπόριο &amp; Διανομή</t>
+        </is>
+      </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
           <t>Block label</t>
@@ -1534,7 +1701,11 @@
           <t>See on map</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr"/>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Δείτε στον χάρτη</t>
+        </is>
+      </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
           <t>Google Maps link</t>
@@ -1552,7 +1723,11 @@
           <t>e-mail</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr"/>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>e-mail</t>
+        </is>
+      </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
           <t>Mailto link text</t>
@@ -1570,7 +1745,11 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr"/>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
           <t>WhatsApp link text</t>
@@ -1588,7 +1767,11 @@
           <t>The vineyard, the cellar, the island. Unfiltered.</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr"/>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Ο αμπελώνας, το οινοποιείο, το νησί. Αφιλτράριστα.</t>
+        </is>
+      </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Sub-note under @nisyroswines handle</t>
@@ -1672,7 +1855,11 @@
           <t>Nisyros · Aegean Sea · Greece</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Νίσυρος · Αιγαίο Πέλαγος · Ελλάδα</t>
+        </is>
+      </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Caption above the wordmark on the hero</t>
@@ -1690,7 +1877,11 @@
           <t>A declaration.</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Μια διακήρυξη.</t>
+        </is>
+      </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Currently unused on site — translate anyway in case it's wired up later</t>
@@ -1715,7 +1906,11 @@
           <t xml:space="preserve">Wines </t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Κρασιά</t>
+        </is>
+      </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Manifesto I — Big title line 1</t>
@@ -1733,7 +1928,11 @@
           <t>from the</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr"/>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>από την</t>
+        </is>
+      </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Manifesto I — Big title line 2</t>
@@ -1751,7 +1950,11 @@
           <t>Edge</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Άκρη</t>
+        </is>
+      </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Manifesto I — Big title line 3 (red accent)</t>
@@ -1769,7 +1972,11 @@
           <t>Nisyros is a Volcano. Alive. It breathes, it trembles, it reminds you who is in charge. We make our wine here — on the edge of the crater.</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Η Νίσυρος είναι Ηφαίστειο. Ζωντανό. Αναπνέει, τρέμει, σου θυμίζει ποιος κουμαντάρει. Φτιάχνουμε εδώ το κρασί μας — στο χείλος του κρατήρα.</t>
+        </is>
+      </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Manifesto I — Body paragraph</t>
@@ -1794,7 +2001,11 @@
           <t>Almost</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Σχεδόν</t>
+        </is>
+      </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Manifesto II — Big title line 1</t>
@@ -1812,7 +2023,11 @@
           <t>Nothing</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Τίποτα</t>
+        </is>
+      </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Manifesto II — Big title line 2 (red accent)</t>
@@ -1844,7 +2059,11 @@
           <t>Minimal intervention in winemaking is a form of love and respect. Our job is to protect without interfering. We step back so the vine can speak.</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr"/>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Η ελάχιστη παρέμβαση στην οινοποίηση είναι μορφή αγάπης και σεβασμού. Δουλειά μας είναι να προστατεύουμε χωρίς να επεμβαίνουμε. Κάνουμε πίσω για να μιλήσει το αμπέλι.</t>
+        </is>
+      </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Manifesto II — Body paragraph</t>
@@ -1869,7 +2088,11 @@
           <t>With the</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Με τη</t>
+        </is>
+      </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Manifesto III — Big title line 1</t>
@@ -1887,7 +2110,11 @@
           <t>Land</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr"/>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Γη</t>
+        </is>
+      </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Manifesto III — Big title line 2 (red accent)</t>
@@ -1905,7 +2132,11 @@
           <t>The volcanic soil of Nisyros is a blessed land. We are guests and, for a moment, caretakers. For millennia agriculture sustained this island. We revive that tradition, with respect and endless dedication. The vine must live here long after we are gone.</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr"/>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Το ηφαιστειακό έδαφος της Νισύρου είναι ευλογημένη γη. Είμαστε φιλοξενούμενοι και, για μια στιγμή, φύλακες. Επί χιλιετίες η γεωργία συντηρούσε αυτό το νησί. Αναβιώνουμε αυτή την παράδοση, με σεβασμό και ατέλειωτη αφοσίωση. Το αμπέλι πρέπει να ζει εδώ πολύ μετά από εμάς.</t>
+        </is>
+      </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Manifesto III — Body paragraph</t>
@@ -1930,7 +2161,11 @@
           <t xml:space="preserve">On the </t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr"/>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Στους</t>
+        </is>
+      </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Manifesto IV — Big title line 1</t>
@@ -1948,7 +2183,11 @@
           <t>Shoulders</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr"/>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Ώμους</t>
+        </is>
+      </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Manifesto IV — Big title line 2</t>
@@ -1966,7 +2205,11 @@
           <t>of Giants</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr"/>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Γιγάντων</t>
+        </is>
+      </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Manifesto IV — Big title line 3 (red accent)</t>
@@ -1984,7 +2227,11 @@
           <t>We read the books, sat with our elders, learned the local traditions. We study fermentation, microbiology, viticulture. And the rules of physics and nature: temperature, pressure, time, climate, seasons. Knowledge is our freedom.</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr"/>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Διαβάσαμε τα βιβλία, καθίσαμε με τους πρεσβύτερους, μάθαμε τις τοπικές παραδόσεις. Μελετάμε ζύμωση, μικροβιολογία, αμπελουργία. Και τους νόμους της φυσικής και της φύσης: θερμοκρασία, πίεση, χρόνος, κλίμα, εποχές. Η γνώση είναι η ελευθερία μας.</t>
+        </is>
+      </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Manifesto IV — Body paragraph</t>
@@ -2009,7 +2256,11 @@
           <t>We try</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Δοκιμάζουμε</t>
+        </is>
+      </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Manifesto V — Big title line 1</t>
@@ -2027,7 +2278,11 @@
           <t>things that</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>πράγματα που</t>
+        </is>
+      </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Manifesto V — Big title line 2</t>
@@ -2045,7 +2300,11 @@
           <t>Fail</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr"/>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Αποτυγχάνουν</t>
+        </is>
+      </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Manifesto V — Big title line 3 (red accent)</t>
@@ -2063,7 +2322,11 @@
           <t>We look for rare vineyards, ferment in unusual vessels, blend the unexpected. Failure is part of making. Essential, so that sometimes, something extraordinary happens. But nothing leaves our cellar unless we are really proud of it.</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr"/>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Ψάχνουμε σπάνιους αμπελώνες, ζυμώνουμε σε ασυνήθιστα δοχεία, αναμιγνύουμε το απρόσμενο. Η αποτυχία είναι μέρος της δημιουργίας. Απαραίτητη, για να συμβεί κάποιες φορές κάτι εξαιρετικό. Αλλά τίποτα δεν φεύγει από το οινοποιείο μας αν δεν είμαστε πραγματικά περήφανοι γι' αυτό.</t>
+        </is>
+      </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Manifesto V — Body paragraph</t>
@@ -2088,7 +2351,11 @@
           <t>We Do</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr"/>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Κάνουμε</t>
+        </is>
+      </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Manifesto VI — Big title line 1</t>
@@ -2106,7 +2373,11 @@
           <t>What we Say</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr"/>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Ό,τι Λέμε</t>
+        </is>
+      </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
           <t>Manifesto VI — Big title line 2 (red accent)</t>
@@ -2125,7 +2396,11 @@
 The bright moments, the dark hours. We do what we say. We say what we do. Trust is part of the bottle.</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr"/>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Μοιραζόμαστε μαζί σας την ιστορία, τον αμπελώνα, τη σοδειά, κάθε βήμα της διαδικασίας.\nΤις φωτεινές στιγμές, τις σκοτεινές ώρες. Κάνουμε ό,τι λέμε. Λέμε ό,τι κάνουμε. Η εμπιστοσύνη είναι μέρος του μπουκαλιού.</t>
+        </is>
+      </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Manifesto VI — Body paragraph. Contains a literal newline.</t>
@@ -2150,7 +2425,11 @@
           <t xml:space="preserve">Message </t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr"/>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Μήνυμα</t>
+        </is>
+      </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
           <t>Credo / Manifesto VII — Big title line 1</t>
@@ -2168,7 +2447,11 @@
           <t xml:space="preserve">in the </t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr"/>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>στο</t>
+        </is>
+      </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
           <t>Credo / Manifesto VII — Big title line 2</t>
@@ -2186,7 +2469,11 @@
           <t>bottle</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr"/>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>μπουκάλι</t>
+        </is>
+      </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
           <t>Credo / Manifesto VII — Big title line 3 (red accent)</t>
@@ -2204,7 +2491,11 @@
           <t>The endless summer. The Aegean light at sunset. The wind, the waves, the freedom. These islands are a gift. So are these wines. Unique, unrepeatable. True to the land. Clean in the glass.</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr"/>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Το ατελείωτο καλοκαίρι. Το φως του Αιγαίου στο ηλιοβασίλεμα. Ο άνεμος, τα κύματα, η ελευθερία. Αυτά τα νησιά είναι δώρο. Όπως και αυτά τα κρασιά. Μοναδικά, ανεπανάληπτα. Πιστά στη γη. Καθαρά στο ποτήρι.</t>
+        </is>
+      </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
           <t>Credo / Manifesto VII — Body paragraph</t>
@@ -2229,7 +2520,11 @@
           <t>We are a small operation on a small island. We answer every message ourselves.</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr"/>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Είμαστε μια μικρή ομάδα σε ένα μικρό νησί. Απαντάμε οι ίδιοι σε κάθε μήνυμα.</t>
+        </is>
+      </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
           <t>Sub-title under "Find Us"</t>
@@ -2247,7 +2542,11 @@
           <t>Nisyros</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr"/>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Νίσυρος</t>
+        </is>
+      </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
           <t>Big value in Location block — "Nisyros" → "Νίσυρος"</t>
@@ -2265,7 +2564,11 @@
           <t>Mandraki village\nNisyros, Dodecanese\nGreece 853 03</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr"/>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Μανδράκι\nΝίσυρος, Δωδεκάνησα\nΕλλάδα 853 03</t>
+        </is>
+      </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
           <t>Address. `\n` = line break, keep them.</t>
@@ -2283,7 +2586,11 @@
           <t>daily@nisyroswines.com</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr"/>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>daily@nisyroswines.com</t>
+        </is>
+      </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
           <t>Email address — DO NOT TRANSLATE (it's the literal mailto target)</t>
@@ -2301,7 +2608,11 @@
           <t>We reply as soon as we can, but we're often out in the vineyard…</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr"/>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Απαντάμε όσο πιο γρήγορα μπορούμε, αλλά συχνά είμαστε στον αμπελώνα…</t>
+        </is>
+      </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
           <t>Sub-note under contact links</t>
@@ -2319,7 +2630,11 @@
           <t>By Appointment</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr"/>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Με Ραντεβού</t>
+        </is>
+      </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
           <t>Big value in Visits block</t>
@@ -2337,7 +2652,11 @@
           <t>We welcome curious visitors. We prefer real conversation over guided tours, so please write to us in advance - especially for tastings. But if you're passing by, knock on the door. If we're around, we'll open it.</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr"/>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Καλωσορίζουμε τους περίεργους επισκέπτες. Προτιμάμε την αληθινή συζήτηση από τις ξεναγήσεις, γι' αυτό γράψτε μας εκ των προτέρων — ιδιαίτερα για γευσιγνωσίες. Αλλά αν περνάτε από εδώ, χτυπήστε την πόρτα. Αν είμαστε γύρω, θα ανοίξουμε.</t>
+        </is>
+      </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
           <t>Sub-note in Visits block</t>
@@ -2355,7 +2674,11 @@
           <t>Limited Allocation</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr"/>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Περιορισμένη Διάθεση</t>
+        </is>
+      </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
           <t>Big value in Trade block</t>
@@ -2373,7 +2696,11 @@
           <t>Production is small and we work with a handful of importers who share our values.</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr"/>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Η παραγωγή είναι μικρή και συνεργαζόμαστε με λίγους εισαγωγείς που μοιράζονται τις αξίες μας.</t>
+        </is>
+      </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
           <t>Sub-note in Trade block</t>
@@ -2391,7 +2718,11 @@
           <t>Nisyros Wines · Dodecanese, Greece · Volcanic Nature</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr"/>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Nisyros Wines · Δωδεκάνησα, Ελλάδα · Ηφαιστειακή Φύση</t>
+        </is>
+      </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
           <t>Page footer. Keep the · separators.</t>
@@ -2416,7 +2747,11 @@
           <t>Three collections. Six wines. Two vintages.</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr"/>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Τρεις συλλογές. Έξι κρασιά. Δύο σοδειές.</t>
+        </is>
+      </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
           <t>Wines page subtitle (not yet wired into HTML — translate anyway)</t>
@@ -2434,7 +2769,11 @@
           <t>Monopàtia</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr"/>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Monopàtia</t>
+        </is>
+      </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
           <t>Collection name — likely stays "Monopàtia"</t>
@@ -2452,7 +2791,11 @@
           <t>A collection of unconventional wines inspired by Dodecanese's old stone paths celebrating creative freedom and authentic uniqueness.</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr"/>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Μια συλλογή ανορθόδοξων κρασιών εμπνευσμένη από τα παλιά πέτρινα μονοπάτια των Δωδεκανήσων, που γιορτάζει τη δημιουργική ελευθερία και την αυθεντική μοναδικότητα.</t>
+        </is>
+      </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Monopàtia description (also appears on Three Directions slide)</t>
@@ -2470,7 +2813,11 @@
           <t>Nereides</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr"/>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Nereides</t>
+        </is>
+      </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
           <t>Collection name — likely stays "Nereides"</t>
@@ -2488,7 +2835,11 @@
           <t>A collection produced with selected grapes from rare Dodecanese vineyards and varieties.</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr"/>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Μια συλλογή που παράγεται από επιλεγμένα σταφύλια σπάνιων αμπελώνων και ποικιλιών των Δωδεκανήσων.</t>
+        </is>
+      </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
           <t>Nereides description (also appears on Three Directions slide)</t>
@@ -2506,7 +2857,11 @@
           <t>Volcanica</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr"/>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Volcanica</t>
+        </is>
+      </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
           <t>Collection name — likely stays "Volcanica"</t>
@@ -2524,7 +2879,11 @@
           <t>Every grape grown and harvested on Nisyros. Pure volcanic terroir, Aegean wind, nothing else.</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr"/>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Κάθε σταφύλι καλλιεργείται και τρυγάται στη Νίσυρο. Καθαρό ηφαιστειακό terroir, αέρας του Αιγαίου, τίποτα άλλο.</t>
+        </is>
+      </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
           <t>Volcanica description (also appears on Three Directions slide)</t>
@@ -2622,7 +2981,11 @@
           <t>3 2 1...</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>3 2 1...</t>
+        </is>
+      </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Wine name (likely stays in original)</t>
@@ -2645,7 +3008,11 @@
           <t>A story unfolds</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Μια ιστορία ξετυλίγεται</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
           <t>One-liner under the wine name</t>
@@ -2668,7 +3035,11 @@
           <t>White</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Λευκό</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Wine type — e.g. White / Rosé / Light Red / Orange</t>
@@ -2691,7 +3062,11 @@
           <t>The moment our winemaking journey truly began: the first time we stood above the vineyards of Mount Attavyros in Embonas, Rhodes, where ancient vines cling to rocky slopes, shaped by time, wind and the hands of generations. Dry-farmed Athiri hand-tended, extremely low yields. Century-old, pre-phylloxera vines growing on cool, sandy-schist soils at 900 meters. || Fermented slowly at low temperatures with indigenous yeasts, aged eight months on the lees. Unfiltered, preserving its natural structure. || Bright. Fragrant. Mineral. Aromas of citrus peel, grapefruit, and orange blossom unfold into notes of almond and fresh bread. Elegant, balanced, vibrant acidity and a long mineral finish. The pure expression of a timeless landscape. Drink it with love. These vines have been waiting a hundred years.</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Η στιγμή που πραγματικά ξεκίνησε το ταξίδι μας στην οινοποίηση: η πρώτη φορά που σταθήκαμε πάνω από τους αμπελώνες του Αττάβυρου στον Έμπωνα της Ρόδου, όπου αρχαία αμπέλια γαντζώνονται σε βραχώδεις πλαγιές, σμιλεμένα από τον χρόνο, τον άνεμο και τα χέρια γενεών. Ξηρικό Αθήρι, καλλιεργημένο με το χέρι, με εξαιρετικά χαμηλές αποδόσεις. Αμπέλια εκατονταετίας, προ φυλλοξήρας, σε δροσερά αμμώδη-σχιστόλιθικα εδάφη στα 900 μέτρα. || Αργή ζύμωση σε χαμηλές θερμοκρασίες με αυτόχθονες ζύμες, παλαίωση οκτώ μηνών στις οινολάσπες. Αφιλτράριστο, διατηρώντας τη φυσική του δομή. || Λαμπερό. Αρωματικό. Μεταλλικό. Αρώματα φλούδας εσπεριδοειδών, γκρέιπφρουτ και άνθους πορτοκαλιάς ξεδιπλώνονται σε νότες αμυγδάλου και φρέσκου ψωμιού. Κομψό, ισορροπημένο, με ζωντανή οξύτητα και μακρά μεταλλική επίγευση. Η καθαρή έκφραση ενός διαχρονικού τοπίου. Πιείτε το με αγάπη. Αυτά τα αμπέλια περιμένουν εκατό χρόνια.</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>3 parts separated by ||  →  Story || Winemaking || Tasting Notes. KEEP the || separators.</t>
@@ -2714,7 +3089,11 @@
           <t>Athiri 100% | Century old ungrafted vines | Minimal intervention | PGI Dodecanese</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Αθήρι 100% | Αμπέλια εκατονταετίας χωρίς εμβολιασμό | Ελάχιστη παρέμβαση | ΠΓΕ Δωδεκανήσου</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Pipe-separated specs shown as small tags. KEEP the | separators between items.</t>
@@ -2737,7 +3116,11 @@
           <t>100% Athiri</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>100% Αθήρι</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Grape varieties — keep latin names (Athiri, Mandilaria…) unless the brand prefers Greek script</t>
@@ -2760,7 +3143,11 @@
           <t>PGI Dodecanese</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>ΠΓΕ Δωδεκανήσου</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Designation — e.g. PGI Dodecanese</t>
@@ -2783,7 +3170,11 @@
           <t>Embonas, Rhodes</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Έμπωνας, Ρόδος</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Vineyard / location</t>
@@ -2806,7 +3197,11 @@
           <t>400-900m</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>400-900μ</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Numbers usually stay (e.g. 400-900m)</t>
@@ -2829,7 +3224,11 @@
           <t>Schist, Sand</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Σχιστόλιθος, Άμμος</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Soil description</t>
@@ -2852,7 +3251,11 @@
           <t>Stainless steel, indigenous yeasts.</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Ανοξείδωτος χάλυβας, αυτόχθονες ζύμες.</t>
+        </is>
+      </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Brief winemaking note</t>
@@ -2875,7 +3278,11 @@
           <t>5000</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Production count — number stays</t>
@@ -2898,7 +3305,11 @@
           <t>2024 | 2025</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>2024 | 2025</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Years separated by `|` — keep numbers and separator</t>
@@ -2921,7 +3332,11 @@
           <t>40 Milia Konda</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>40 Milia Konda</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Wine name (likely stays in original)</t>
@@ -2944,7 +3359,11 @@
           <t>A shared table</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Ένα κοινό τραπέζι</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
           <t>One-liner under the wine name</t>
@@ -2967,7 +3386,11 @@
           <t>Semi-sparkling Rosé</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Ημιαφρώδες Ροζέ</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
           <t>Wine type — e.g. White / Rosé / Light Red / Orange</t>
@@ -2990,7 +3413,11 @@
           <t>Forty miles of open sea separate our winery from the old vineyard where these grapes are grown. The farmers who kept those vines alive through generations became family. Between us, forty miles feel like a shared table. Konda: near, not far. || 95% Athiri, 5% Mandilaria from the vineyards of Siana and Embonas, Rhodes. Blend of cellar techniques: brief skin maceration, white vinification of red grapes, and light carbonic maceration. Spontaneous fermentation with indigenous yeasts. Refermented in bottle. || Pale pink, delicate, alive. Floral notes, white-fleshed fruit, a whisper of red berries. Fresh, juicy, with a fine natural sparkle and a clean saline finish. Pair it with the sound of waves and fresh wind.</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Σαράντα μίλια ανοιχτής θάλασσας χωρίζουν το οινοποιείο μας από τον παλιό αμπελώνα όπου καλλιεργούνται αυτά τα σταφύλια. Οι αγρότες που κράτησαν αυτά τα αμπέλια ζωντανά μέσα από γενιές έγιναν οικογένεια. Ανάμεσά μας, σαράντα μίλια μοιάζουν με ένα κοινό τραπέζι. Konda: κοντά, όχι μακριά. || 95% Αθήρι, 5% Μανδηλαριά από τους αμπελώνες της Σιάννας και του Έμπωνα στη Ρόδο. Συνδυασμός τεχνικών οινοποιείου: σύντομη εκχύλιση φλούδας, λευκή οινοποίηση ερυθρών σταφυλιών και ελαφριά ανθρακική εκχύλιση. Αυθόρμητη ζύμωση με αυτόχθονες ζύμες. Επαναζύμωση σε φιάλη. || Απαλό ροζ, λεπτό, ζωντανό. Λουλουδάτες νότες, φρούτα με λευκή σάρκα, ένας ψίθυρος κόκκινων μούρων. Φρέσκο, ζουμερό, με λεπτή φυσική φυσαλίδα και καθαρή αλατούχα επίγευση. Συνοδέψτε το με τον ήχο των κυμάτων και τον φρέσκο αέρα.</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
           <t>3 parts separated by ||  →  Story || Winemaking || Tasting Notes. KEEP the || separators.</t>
@@ -3013,7 +3440,11 @@
           <t>Mandilaria · Athiri | Co-fermented | Volcanic iron soil | Minimal SO₂ | Monopatia collection | Sparkling</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Μανδηλαριά · Αθήρι | Συνζύμωση | Ηφαιστειακό σιδηρούχο έδαφος | Ελάχιστο SO₂ | Συλλογή Monopàtia | Αφρώδες</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Pipe-separated specs shown as small tags. KEEP the | separators between items.</t>
@@ -3036,7 +3467,11 @@
           <t>95% Athiri, 5% Mandilaria</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>95% Αθήρι, 5% Μανδηλαριά</t>
+        </is>
+      </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Grape varieties — keep latin names (Athiri, Mandilaria…) unless the brand prefers Greek script</t>
@@ -3059,7 +3494,11 @@
           <t>PGI Dodecanese</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>ΠΓΕ Δωδεκανήσου</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Designation — e.g. PGI Dodecanese</t>
@@ -3082,7 +3521,11 @@
           <t>Siana, Embonas, Rhodes</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Σιάννα, Έμπωνας, Ρόδος</t>
+        </is>
+      </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
           <t>Vineyard / location</t>
@@ -3105,7 +3548,11 @@
           <t>150m</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>150μ</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Numbers usually stay (e.g. 400-900m)</t>
@@ -3128,7 +3575,11 @@
           <t>Volcanic and sandy</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Ηφαιστειακό και αμμώδες</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
           <t>Soil description</t>
@@ -3151,7 +3602,11 @@
           <t>Brief skin contact. Light carbonic maceration. Spontaneous fermentation.</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Σύντομη επαφή με τη φλούδα. Ελαφριά ανθρακική εκχύλιση. Αυθόρμητη ζύμωση.</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Brief winemaking note</t>
@@ -3174,7 +3629,11 @@
           <t>1800</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
           <t>Production count — number stays</t>
@@ -3197,7 +3656,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
           <t>Years separated by `|` — keep numbers and separator</t>
@@ -3220,7 +3683,11 @@
           <t>Roudià</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Roudià</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
           <t>Wine name (likely stays in original)</t>
@@ -3243,7 +3710,11 @@
           <t>The tree of life</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Το δέντρο της ζωής</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
           <t>One-liner under the wine name</t>
@@ -3266,7 +3737,11 @@
           <t>Light Red</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Ελαφρύ Ερυθρό</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
           <t>Wine type — e.g. White / Rosé / Light Red / Orange</t>
@@ -3289,7 +3764,11 @@
           <t>In the Dodecanese, the pomegranate is called 'roudia.' In Greek myth and memory, it has always been the fruit of life and return — eaten by Persephone, offered at weddings, broken open at thresholds for luck. Each one holds a hundred seeds, a hundred small promises. Like its fruit, this wine reveals a deep, jewelled red: dense, alive, generous.|| Mandilaria and Athiri from old dry-farmed vines on the volcanic sandy soils of Siana, Rhodes. Harvested early to preserve natural acidity and pure fruit energy. Semi-carbonic maceration to enhance the primary aromatic profile. Spontaneous fermentation in stainless steel with indigenous yeasts. Unfined. 8 months in stainless steel. || An explosion of fresh small red fruits — redcurrant, mulberry, a delicate touch of cherry. Snappy, light, thirst-quenching. Vibrant acidity, delicate tannins. Drink chilled. Here's to life, here's to endless summer sunsets.</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Στα Δωδεκάνησα, το ρόδι λέγεται «ροδιά». Στον ελληνικό μύθο και τη μνήμη, ήταν πάντα ο καρπός της ζωής και της επιστροφής — που έφαγε η Περσεφόνη, που προσφέρεται στους γάμους, που σπάει στα κατώφλια για τύχη. Καθένα κρατά εκατό σπόρους, εκατό μικρές υποσχέσεις. Όπως ο καρπός του, αυτό το κρασί αποκαλύπτει ένα βαθύ, διαμαντένιο κόκκινο: πυκνό, ζωντανό, γενναιόδωρο. || Μανδηλαριά και Αθήρι από παλιά ξηρικά αμπέλια στα ηφαιστειακά αμμώδη εδάφη της Σιάννας, Ρόδος. Πρώιμος τρύγος για τη διατήρηση της φυσικής οξύτητας και της καθαρής φρουτώδους ενέργειας. Ημι-ανθρακική εκχύλιση για την ανάδειξη του πρωτογενούς αρωματικού προφίλ. Αυθόρμητη ζύμωση σε ανοξείδωτο χάλυβα με αυτόχθονες ζύμες. Χωρίς κολλάρισμα. 8 μήνες σε ανοξείδωτο χάλυβα. || Μια έκρηξη φρέσκων μικρών κόκκινων φρούτων — φραγκοστάφυλο, μουριά, μια λεπτή πινελιά κερασιού. Νευρώδες, ελαφρύ, δροσιστικό. Ζωντανή οξύτητα, λεπτές τανίνες. Πίνεται παγωμένο. Στη ζωή, στα ατελείωτα καλοκαιρινά ηλιοβασιλέματα.</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
           <t>3 parts separated by ||  →  Story || Winemaking || Tasting Notes. KEEP the || separators.</t>
@@ -3312,7 +3791,11 @@
           <t>Mavrothiriko · Assyrtiko | Dry-farmed old vines | Volcanic terraces | PGI Dodecanese</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Μαυροθήρικο · Ασύρτικο | Ξηρικά παλιά αμπέλια | Ηφαιστειακές αναβαθμίδες | ΠΓΕ Δωδεκανήσου</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
           <t>Pipe-separated specs shown as small tags. KEEP the | separators between items.</t>
@@ -3335,7 +3818,11 @@
           <t>70% Mandilaria, 30% Athiri</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>70% Μανδηλαριά, 30% Αθήρι</t>
+        </is>
+      </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
           <t>Grape varieties — keep latin names (Athiri, Mandilaria…) unless the brand prefers Greek script</t>
@@ -3358,7 +3845,11 @@
           <t>PGI Dodecanese</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>ΠΓΕ Δωδεκανήσου</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
           <t>Designation — e.g. PGI Dodecanese</t>
@@ -3381,7 +3872,11 @@
           <t>Siana, Embonas, Rhodes</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Σιάννα, Έμπωνας, Ρόδος</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
           <t>Vineyard / location</t>
@@ -3404,7 +3899,11 @@
           <t>150m</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>150μ</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
           <t>Numbers usually stay (e.g. 400-900m)</t>
@@ -3427,7 +3926,11 @@
           <t>Volcanic and sandy</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Ηφαιστειακό και αμμώδες</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
           <t>Soil description</t>
@@ -3450,7 +3953,11 @@
           <t>Semi-carbonic maceration. Spontaneous fermentation in stainless steel tanks. Unfined.</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Ημι-ανθρακική εκχύλιση. Αυθόρμητη ζύμωση σε ανοξείδωτες δεξαμενές. Χωρίς κολλάρισμα.</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
           <t>Brief winemaking note</t>
@@ -3473,7 +3980,11 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
           <t>Production count — number stays</t>
@@ -3496,7 +4007,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
           <t>Years separated by `|` — keep numbers and separator</t>
@@ -3526,7 +4041,11 @@
           <t>Apiri</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Apiri</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
           <t>Wine name (likely stays in original)</t>
@@ -3549,7 +4068,11 @@
           <t>Amphora</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Αμφορέας</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
           <t>One-liner under the wine name</t>
@@ -3572,7 +4095,11 @@
           <t>Orange</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Πορτοκαλί</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
           <t>Wine type — e.g. White / Rosé / Light Red / Orange</t>
@@ -3596,7 +4123,12 @@
 exotic fruits, honey, dried apricot, toasted almond, and soft tobacco. On the palate, it’s broad, slightly saline, with gentle tannins and lively acidity, finishing long and textured. A wine for curious drinkers and bold food pairings.</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Ο ζεστός αέρας που αναπνέει μέσα από τις σχισμές του ηφαιστείου — ακόμη και μέσα στα χωριά, στα σπίτια — λέγεται Apyri. Αυτό το κρασί παίρνει το όνομά του από αυτή την ανάσα. || Ελαφριά μερική εκχύλιση φλούδας για αρωματική πολυπλοκότητα· το υπόλοιπο πιέζεται απευθείας για φρεσκάδα και τραγανότητα. Ζύμωση σε ανοξείδωτο χάλυβα και αμφορείς με αυτόχθονες ζύμες. Χωρίς κολλάρισμα. Παλαίωση σε αμφορέα. || Εξελισσόμενα αρώματα λουλουδάτων και
+εξωτικών φρούτων, μέλι, αποξηραμένο βερίκοκο, καβουρδισμένο αμύγδαλο και απαλό καπνό. Στον ουρανίσκο, ευρύ, ελαφρώς αλατούχο, με ήπιες τανίνες και ζωντανή οξύτητα, καταλήγει μακρύ και με υφή. Ένα κρασί για περίεργους πότες και τολμηρούς συνδυασμούς φαγητού.</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
           <t>3 parts separated by ||  →  Story || Winemaking || Tasting Notes. KEEP the || separators.</t>
@@ -3619,7 +4151,11 @@
           <t>Athiri blend | Partial skin contact | Spontaneous fermatation | Amphora | Unclarified  | Unfiltered</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Μείγμα Αθήρι | Μερική επαφή με φλούδα | Αυθόρμητη ζύμωση | Αμφορέας | Χωρίς διαύγαση | Αφιλτράριστο</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
           <t>Pipe-separated specs shown as small tags. KEEP the | separators between items.</t>
@@ -3642,7 +4178,11 @@
           <t>100% Athiri</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>100% Αθήρι</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
           <t>Grape varieties — keep latin names (Athiri, Mandilaria…) unless the brand prefers Greek script</t>
@@ -3665,7 +4205,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr"/>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
           <t>Designation — e.g. PGI Dodecanese</t>
@@ -3688,7 +4232,11 @@
           <t>Embonas, Rhodes</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Έμπωνας, Ρόδος</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
           <t>Vineyard / location</t>
@@ -3711,7 +4259,11 @@
           <t>400-900m</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr"/>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>400-900μ</t>
+        </is>
+      </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
           <t>Numbers usually stay (e.g. 400-900m)</t>
@@ -3734,7 +4286,11 @@
           <t>Schist, Sand</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Σχιστόλιθος, Άμμος</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
           <t>Soil description</t>
@@ -3757,7 +4313,11 @@
           <t>Two-week skin maceration. Fermentation in stainless steel and anmphoras. Indigenous yeasts.</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr"/>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Δεκαπενθήμερη εκχύλιση φλούδας. Ζύμωση σε ανοξείδωτο χάλυβα και αμφορείς. Αυτόχθονες ζύμες.</t>
+        </is>
+      </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
           <t>Brief winemaking note</t>
@@ -3780,7 +4340,11 @@
           <t>3000</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr"/>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
           <t>Production count — number stays</t>
@@ -3803,7 +4367,11 @@
           <t>2024 | 2025</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>2024 | 2025</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
           <t>Years separated by `|` — keep numbers and separator</t>
@@ -3826,7 +4394,11 @@
           <t>Atmida</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr"/>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Atmida</t>
+        </is>
+      </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
           <t>Wine name (likely stays in original)</t>
@@ -3849,7 +4421,11 @@
           <t>Volcanic nature</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Ηφαιστειακή φύση</t>
+        </is>
+      </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
           <t>One-liner under the wine name</t>
@@ -3872,7 +4448,11 @@
           <t>Rosé</t>
         </is>
       </c>
-      <c r="D60" s="8" t="inlineStr"/>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Ροζέ</t>
+        </is>
+      </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
           <t>Wine type — e.g. White / Rosé / Light Red / Orange</t>
@@ -3895,7 +4475,11 @@
           <t>Atmida: the steam vapour that rises from the ground on cool mornings. A quiet reminder of who runs the place. This is our first wine made entirely with grapes grown on Nisyros. We could not be prouder. || Two varieties, harvested with opposite logic: Mavrothiriko picked early for acidity, Assyrtiko picked late for structure and complexity. Hand-destemmed, foot-crushed in the time-honoured tradition. Fermentation with indigenous yeasts. Unfined. 8 months in terracotta amphora. || Pale, bright, transparent red. Wild strawberry, small red fruits, deep earthy and mineral scents — the direct legacy of the volcanic soil. Vibrant acidity meets warmth and savoriness. The finish is tense, fresh, and distinctly mineral. Drink it slightly chilled. This is our meditative wine: give it time, and the volcano will speak."</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr"/>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Atmida: ο ατμός που υψώνεται από το έδαφος τα δροσερά πρωινά. Μια ήσυχη υπενθύμιση για το ποιος κουμαντάρει εδώ. Αυτό είναι το πρώτο μας κρασί φτιαγμένο εξ ολοκλήρου με σταφύλια από τη Νίσυρο. Δεν θα μπορούσαμε να είμαστε πιο περήφανοι. || Δύο ποικιλίες, που τρυγήθηκαν με αντίθετη λογική: Μαυροθήρικο πρώιμα για την οξύτητα, Ασύρτικο όψιμα για τη δομή και την πολυπλοκότητα. Αποβοστρύχωση με το χέρι, πατητήρι με τα πόδια κατά την παλαιά παράδοση. Ζύμωση με αυτόχθονες ζύμες. Χωρίς κολλάρισμα. 8 μήνες σε πήλινο αμφορέα. || Απαλό, λαμπερό, διάφανο κόκκινο. Άγρια φράουλα, μικρά κόκκινα φρούτα, βαθιά γήινα και μεταλλικά αρώματα — η άμεση κληρονομιά του ηφαιστειακού εδάφους. Η ζωντανή οξύτητα συναντά τη ζεστασιά και τη γευστικότητα. Η επίγευση είναι έντονη, φρέσκια και ξεκάθαρα μεταλλική. Πίνεται ελαφρώς παγωμένο. Αυτό είναι το διαλογιστικό μας κρασί: δώστε του χρόνο, και το ηφαίστειο θα μιλήσει.</t>
+        </is>
+      </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
           <t>3 parts separated by ||  →  Story || Winemaking || Tasting Notes. KEEP the || separators.</t>
@@ -3918,7 +4502,11 @@
           <t>Assyrtiko · Mavrothiriko | Wild ferment | Unclarified | Foot-crushed</t>
         </is>
       </c>
-      <c r="D62" s="8" t="inlineStr"/>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Ασύρτικο · Μαυροθήρικο | Άγρια ζύμωση | Χωρίς διαύγαση | Πατημένο με τα πόδια</t>
+        </is>
+      </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
           <t>Pipe-separated specs shown as small tags. KEEP the | separators between items.</t>
@@ -3941,7 +4529,11 @@
           <t>60% Assyrtiko, 40% Mavrothiriko</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr"/>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>60% Ασύρτικο, 40% Μαυροθήρικο</t>
+        </is>
+      </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
           <t>Grape varieties — keep latin names (Athiri, Mandilaria…) unless the brand prefers Greek script</t>
@@ -3964,7 +4556,11 @@
           <t>PGI Dodecanese</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>ΠΓΕ Δωδεκανήσου</t>
+        </is>
+      </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
           <t>Designation — e.g. PGI Dodecanese</t>
@@ -3987,7 +4583,11 @@
           <t>Nisyros</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr"/>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Νίσυρος</t>
+        </is>
+      </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
           <t>Vineyard / location</t>
@@ -4010,7 +4610,11 @@
           <t>400m</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>400μ</t>
+        </is>
+      </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
           <t>Numbers usually stay (e.g. 400-900m)</t>
@@ -4033,7 +4637,11 @@
           <t>Volcanic, rich in minerals</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr"/>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Ηφαιστειακό, πλούσιο σε μέταλλα</t>
+        </is>
+      </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
           <t>Soil description</t>
@@ -4056,7 +4664,11 @@
           <t>Crushed by foot. Indigenous yeasts. Aged in Amphora. Unfined.</t>
         </is>
       </c>
-      <c r="D68" s="8" t="inlineStr"/>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Πατημένο με τα πόδια. Αυτόχθονες ζύμες. Παλαιωμένο σε Αμφορέα. Χωρίς κολλάρισμα.</t>
+        </is>
+      </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
           <t>Brief winemaking note</t>
@@ -4079,7 +4691,11 @@
           <t>500</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
           <t>Production count — number stays</t>
@@ -4102,7 +4718,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D70" s="8" t="inlineStr"/>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
           <t>Years separated by `|` — keep numbers and separator</t>
@@ -4185,7 +4805,11 @@
           <t>Landscape</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Τοπίο</t>
+        </is>
+      </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4208,7 +4832,11 @@
           <t>Vulcanic Nature.</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Ηφαιστειακή Φύση.</t>
+        </is>
+      </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4231,7 +4859,11 @@
           <t>Winery</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Οινοποιείο</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4254,7 +4886,11 @@
           <t>Clay and time.</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Πηλός και χρόνος.</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4277,7 +4913,11 @@
           <t>Winery</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Οινοποιείο</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4300,7 +4940,11 @@
           <t>By foot. Like they did.</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Με τα πόδια. Όπως έκαναν.</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4323,7 +4967,11 @@
           <t>Harvest</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Τρύγος</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4346,7 +4994,11 @@
           <t>Federico.</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Federico.</t>
+        </is>
+      </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4369,7 +5021,11 @@
           <t>Harvest</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Τρύγος</t>
+        </is>
+      </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4392,7 +5048,11 @@
           <t>Friends when it matters.</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Φίλοι όταν μετράει.</t>
+        </is>
+      </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4415,7 +5075,11 @@
           <t>People</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Άνθρωποι</t>
+        </is>
+      </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4438,7 +5102,11 @@
           <t>Feet in the dirt. That's enough.</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Πόδια στο χώμα. Αυτό φτάνει.</t>
+        </is>
+      </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4461,7 +5129,11 @@
           <t>Territory</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Επικράτεια</t>
+        </is>
+      </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4484,7 +5156,11 @@
           <t>Life everywhere.</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Ζωή παντού.</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4507,7 +5183,11 @@
           <t>Winery</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Οινοποιείο</t>
+        </is>
+      </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4530,7 +5210,11 @@
           <t>Aging, slowly.</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Παλαιώνει, αργά.</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4553,7 +5237,11 @@
           <t>Territory</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Επικράτεια</t>
+        </is>
+      </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4576,7 +5264,11 @@
           <t>The island has its own mind.</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Το νησί έχει δικό του μυαλό.</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4599,7 +5291,11 @@
           <t>Vineyard</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Αμπελώνας</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4622,7 +5318,11 @@
           <t>Embonas, in Rhodes.</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Έμπωνας, στη Ρόδο.</t>
+        </is>
+      </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4645,7 +5345,11 @@
           <t>Harvest</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Τρύγος</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4668,7 +5372,11 @@
           <t>Guests.</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Καλεσμένοι.</t>
+        </is>
+      </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4691,7 +5399,11 @@
           <t>People</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Άνθρωποι</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4714,7 +5426,11 @@
           <t>Bicycles, always.</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Ποδήλατα, πάντα.</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4737,7 +5453,11 @@
           <t>People</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Άνθρωποι</t>
+        </is>
+      </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4760,7 +5480,11 @@
           <t>Federico Garzelli. Winemaker.</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Federico Garzelli. Οινοποιός.</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4783,7 +5507,11 @@
           <t>Territory</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Επικράτεια</t>
+        </is>
+      </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4806,7 +5534,11 @@
           <t>Life, life.</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Ζωή, ζωή.</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4829,7 +5561,11 @@
           <t>Planting</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Φύτευση</t>
+        </is>
+      </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4852,7 +5588,11 @@
           <t>Slowly.</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Αργά.</t>
+        </is>
+      </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4875,7 +5615,11 @@
           <t>People</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Άνθρωποι</t>
+        </is>
+      </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4898,7 +5642,11 @@
           <t>No rest.</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Καμία ξεκούραση.</t>
+        </is>
+      </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4921,7 +5669,11 @@
           <t>Winery</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Οινοποιείο</t>
+        </is>
+      </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4944,7 +5696,11 @@
           <t>Still becoming.</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Ακόμη γίνεται.</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -4967,7 +5723,11 @@
           <t>Harvest</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr"/>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Τρύγος</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -4990,7 +5750,11 @@
           <t>All together.</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Όλοι μαζί.</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -5013,7 +5777,11 @@
           <t>Harvest</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Τρύγος</t>
+        </is>
+      </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -5036,7 +5804,11 @@
           <t>First press.</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Πρώτη πίεση.</t>
+        </is>
+      </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -5059,7 +5831,11 @@
           <t>Planting</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Φύτευση</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -5082,7 +5858,11 @@
           <t>Planting seeds...</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Φυτεύοντας σπόρους...</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -5105,7 +5885,11 @@
           <t>Planting</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Φύτευση</t>
+        </is>
+      </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -5128,7 +5912,11 @@
           <t>Generations.</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Γενιές.</t>
+        </is>
+      </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -5151,7 +5939,11 @@
           <t>Landscape</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr"/>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Τοπίο</t>
+        </is>
+      </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -5174,7 +5966,11 @@
           <t>The Aegean holds the light.</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Το Αιγαίο κρατά το φως.</t>
+        </is>
+      </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -5197,7 +5993,11 @@
           <t>People</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr"/>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Άνθρωποι</t>
+        </is>
+      </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -5220,7 +6020,11 @@
           <t>Theologos. Body and soul.</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Θεολόγος. Σώμα και ψυχή.</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -5243,7 +6047,11 @@
           <t>Territory</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr"/>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Επικράτεια</t>
+        </is>
+      </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -5266,7 +6074,11 @@
           <t xml:space="preserve">Aloni - the traditional mill. </t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr"/>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Αλώνι — ο παραδοσιακός μύλος.</t>
+        </is>
+      </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -5289,7 +6101,11 @@
           <t>Landscape</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Τοπίο</t>
+        </is>
+      </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -5312,7 +6128,11 @@
           <t>It boils.</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr"/>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Βράζει.</t>
+        </is>
+      </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -5335,7 +6155,11 @@
           <t>People</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Άνθρωποι</t>
+        </is>
+      </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -5358,7 +6182,11 @@
           <t>Giorgos and Nicola, 2020. "What if..."</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr"/>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Γιώργος και Nicola, 2020. «Κι αν…»</t>
+        </is>
+      </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -5381,7 +6209,11 @@
           <t>Winery</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr"/>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Οινοποιείο</t>
+        </is>
+      </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
           <t>Short caption shown over the photo in the lightbox (e.g. Landscape, Winery, Harvest, People). Some labels repeat across photos.</t>
@@ -5404,7 +6236,11 @@
           <t>Almost ready.</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Σχεδόν έτοιμο.</t>
+        </is>
+      </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
           <t>One-line caption under the label.</t>
@@ -5474,7 +6310,11 @@
           <t>Nisyros Wines — Volcanic Natural Wines from the Aegean Sea</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Nisyros Wines — Ηφαιστειακά Φυσικά Κρασιά από το Αιγαίο</t>
+        </is>
+      </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
           <t>&lt;title&gt; tag — try to stay under ~65 chars in Greek</t>
@@ -5492,7 +6332,11 @@
           <t>Small producer of natural wines on Nisyros, a volcanic island in the Dodecanese, Greece. Indigenous grape varieties, minimal intervention, volcanic terroir.</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Μικρός παραγωγός φυσικών κρασιών στη Νίσυρο, ηφαιστειογενές νησί στα Δωδεκάνησα. Αυτόχθονες ποικιλίες, ελάχιστη παρέμβαση, ηφαιστειακό terroir.</t>
+        </is>
+      </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>&lt;meta description&gt;. A draft Greek version already exists in head.html — review and refine: "Μικρός παραγωγός φυσικών κρασιών στη Νίσυρο, ηφαιστειογενές νησί στα Δωδεκάνησα. Αυτόχθονες ποικιλίες, ελάχιστη παρέμβαση, ηφαιστειακό terroir."</t>
@@ -5510,7 +6354,11 @@
           <t>natural wines Greece, volcanic wines, Aegean wines, Nisyros, Dodecanese wines, Greek natural wine producer</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>φυσικά κρασιά Ελλάδα, ηφαιστειακά κρασιά, κρασιά Αιγαίου, Νίσυρος, Δωδεκάνησα, Ελληνικά φυσικά κρασιά</t>
+        </is>
+      </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
           <t>&lt;meta keywords&gt;. Greek draft already in head.html: "φυσικά κρασιά Ελλάδα, ηφαιστειακά κρασιά, κρασιά Αιγαίου, Νίσυρος, Δωδεκάνησα, Ελληνικά φυσικά κρασιά"</t>
@@ -5528,7 +6376,11 @@
           <t>Nisyros Wines — Volcanic Natural Wines from the Aegean Sea</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr"/>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Nisyros Wines — Ηφαιστειακά Φυσικά Κρασιά από το Αιγαίο</t>
+        </is>
+      </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Open Graph title (social share preview). Usually = seo.title.</t>
@@ -5546,7 +6398,11 @@
           <t>Small producer of natural wines on Nisyros, a volcanic island in the Dodecanese, Greece.</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Μικρός παραγωγός φυσικών κρασιών στη Νίσυρο, ηφαιστειογενές νησί στα Δωδεκάνησα.</t>
+        </is>
+      </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Open Graph description (shorter than seo.description).</t>
@@ -5564,7 +6420,11 @@
           <t>en_GB</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr"/>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>el_GR</t>
+        </is>
+      </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
           <t>For Greek version use `el_GR` — fixed value, no translation.</t>
@@ -5582,7 +6442,11 @@
           <t>Small producer of natural wines on Nisyros, a volcanic island in the Dodecanese, Greece. Indigenous grape varieties, minimal intervention, volcanic terroir.</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Μικρός παραγωγός φυσικών κρασιών στη Νίσυρο, ηφαιστειογενές νησί στα Δωδεκάνησα. Αυτόχθονες ποικιλίες, ελάχιστη παρέμβαση, ηφαιστειακό terroir.</t>
+        </is>
+      </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Schema.org Winery `description`. Usually = seo.description.</t>
